--- a/sheets/조재수대금교본/검수/대왕의 길.xlsx
+++ b/sheets/조재수대금교본/검수/대왕의 길.xlsx
@@ -4326,7 +4326,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
+          <t xml:space="preserve">㳞
 –㴌</t>
         </is>
       </c>
@@ -4368,8 +4368,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -4408,41 +4407,24 @@
         </is>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21"/>
       <c r="M5" s="24"/>
     </row>
     <row r="6" ht="90.2" customHeight="true">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B6" s="21"/>
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E6" s="22"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
@@ -4460,7 +4442,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
+          <t xml:space="preserve">㳞
 –汰</t>
         </is>
       </c>
@@ -4471,8 +4453,7 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C7" s="23"/>
@@ -4485,7 +4466,7 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
+          <t xml:space="preserve">㳞
 –㳞</t>
         </is>
       </c>
@@ -4515,7 +4496,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="C8" s="24"/>
@@ -4528,8 +4509,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -4564,17 +4544,9 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21"/>
       <c r="I9" s="22"/>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J9" s="21"/>
       <c r="K9" s="22"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L9" s="21"/>
       <c r="M9" s="22"/>
     </row>
     <row r="10" ht="90.2" customHeight="true">
@@ -4586,16 +4558,11 @@
         </is>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G10" s="23"/>
@@ -4636,7 +4603,7 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
+          <t xml:space="preserve">㳞
 –㳞</t>
         </is>
       </c>
@@ -4682,8 +4649,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -4721,17 +4687,9 @@
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="23"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L13" s="21"/>
       <c r="M13" s="23"/>
     </row>
     <row r="14" ht="90.2" customHeight="true">
@@ -4740,21 +4698,15 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -4768,7 +4720,7 @@
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-–h</t>
+–</t>
         </is>
       </c>
       <c r="M14" s="24"/>
@@ -4821,8 +4773,7 @@
       <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-㳞∼
-‹</t>
+㳞∼</t>
         </is>
       </c>
       <c r="K17" s="22"/>
@@ -4851,7 +4802,7 @@
       <c r="G18" s="23"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㅂ∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="I18" s="23"/>
@@ -4886,24 +4837,18 @@
         </is>
       </c>
       <c r="G19" s="24"/>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H19" s="21"/>
       <c r="I19" s="24"/>
       <c r="J19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="K19" s="24"/>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M19" s="24"/>
@@ -4977,18 +4922,9 @@
       <c r="E22" s="24"/>
       <c r="F22" s="21"/>
       <c r="G22" s="24"/>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅂ
-‹</t>
-        </is>
-      </c>
+      <c r="H22" s="21"/>
       <c r="I22" s="24"/>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J22" s="21"/>
       <c r="K22" s="24"/>
       <c r="L22" s="21"/>
       <c r="M22" s="24"/>
@@ -5015,16 +4951,11 @@
       <c r="J23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-淋∼
-‹</t>
+淋∼</t>
         </is>
       </c>
       <c r="K23" s="22"/>
-      <c r="L23" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L23" s="21"/>
       <c r="M23" s="22"/>
     </row>
     <row r="24" ht="90.2" customHeight="true">
@@ -5073,23 +5004,20 @@
       <c r="G25" s="24"/>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="24"/>
       <c r="J25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="K25" s="24"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M25" s="24"/>
@@ -5135,11 +5063,7 @@
       <c r="E27" s="23"/>
       <c r="F27" s="21"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅂ</t>
-        </is>
-      </c>
+      <c r="H27" s="21"/>
       <c r="I27" s="23"/>
       <c r="J27" s="21"/>
       <c r="K27" s="23"/>
@@ -5160,17 +5084,9 @@
       <c r="G28" s="24"/>
       <c r="H28" s="21"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L28" s="21"/>
       <c r="M28" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/대왕의 길.xlsx
+++ b/sheets/조재수대금교본/검수/대왕의 길.xlsx
@@ -4326,7 +4326,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄱ
 –㴌</t>
         </is>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄱ
 –汰</t>
         </is>
       </c>
@@ -4466,7 +4466,7 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄱ
 –㳞</t>
         </is>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="C8" s="24"/>
@@ -4603,7 +4603,7 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄱ
 –㳞</t>
         </is>
       </c>
@@ -4720,7 +4720,7 @@
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-–</t>
+–h</t>
         </is>
       </c>
       <c r="M14" s="24"/>
@@ -4802,7 +4802,7 @@
       <c r="G18" s="23"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">ㅂ∼</t>
         </is>
       </c>
       <c r="I18" s="23"/>
@@ -4922,7 +4922,11 @@
       <c r="E22" s="24"/>
       <c r="F22" s="21"/>
       <c r="G22" s="24"/>
-      <c r="H22" s="21"/>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅂ</t>
+        </is>
+      </c>
       <c r="I22" s="24"/>
       <c r="J22" s="21"/>
       <c r="K22" s="24"/>
@@ -5004,7 +5008,8 @@
       <c r="G25" s="24"/>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="I25" s="24"/>
@@ -5017,7 +5022,8 @@
       <c r="K25" s="24"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="M25" s="24"/>
@@ -5063,7 +5069,11 @@
       <c r="E27" s="23"/>
       <c r="F27" s="21"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="21"/>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅂ</t>
+        </is>
+      </c>
       <c r="I27" s="23"/>
       <c r="J27" s="21"/>
       <c r="K27" s="23"/>

--- a/sheets/조재수대금교본/검수/대왕의 길.xlsx
+++ b/sheets/조재수대금교본/검수/대왕의 길.xlsx
@@ -4279,24 +4279,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="71.62" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="71.62" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
       <c r="L4" s="21"/>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="71.62" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
       <c r="L5" s="21"/>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="71.62" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="71.62" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="71.62" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="71.62" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       <c r="L9" s="21"/>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="71.62" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="M10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="71.62" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="71.62" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4658,7 +4658,7 @@
       <c r="L12" s="21"/>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="71.62" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
       <c r="L13" s="21"/>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="71.62" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4728,7 +4728,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60.61" customHeight="true">
+    <row r="16" ht="48.19" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       <c r="L16" s="20"/>
       <c r="M16" s="20"/>
     </row>
-    <row r="17" ht="90.2" customHeight="true">
+    <row r="17" ht="71.62" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="M17" s="22"/>
     </row>
-    <row r="18" ht="90.2" customHeight="true">
+    <row r="18" ht="71.62" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="M18" s="23"/>
     </row>
-    <row r="19" ht="90.2" customHeight="true">
+    <row r="19" ht="71.62" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="M19" s="24"/>
     </row>
-    <row r="20" ht="90.2" customHeight="true">
+    <row r="20" ht="71.62" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="M20" s="22"/>
     </row>
-    <row r="21" ht="90.2" customHeight="true">
+    <row r="21" ht="71.62" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -4914,7 +4914,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="23"/>
     </row>
-    <row r="22" ht="90.2" customHeight="true">
+    <row r="22" ht="71.62" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -4933,7 +4933,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="24"/>
     </row>
-    <row r="23" ht="90.2" customHeight="true">
+    <row r="23" ht="71.62" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -4962,7 +4962,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" ht="90.2" customHeight="true">
+    <row r="24" ht="71.62" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="M24" s="23"/>
     </row>
-    <row r="25" ht="90.2" customHeight="true">
+    <row r="25" ht="71.62" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="M25" s="24"/>
     </row>
-    <row r="26" ht="90.2" customHeight="true">
+    <row r="26" ht="71.62" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="M26" s="22"/>
     </row>
-    <row r="27" ht="90.2" customHeight="true">
+    <row r="27" ht="71.62" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -5080,7 +5080,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="23"/>
     </row>
-    <row r="28" ht="90.2" customHeight="true">
+    <row r="28" ht="71.62" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -5106,7 +5106,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
